--- a/Assets/Ressources/Stats/Crew_stats.xlsx
+++ b/Assets/Ressources/Stats/Crew_stats.xlsx
@@ -1,25 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10609BD0-D3E6-4898-94A8-A1CB9524523A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>ATK</t>
+  </si>
+  <si>
+    <t>Crit Rate</t>
+  </si>
+  <si>
+    <t>Crit DMG</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Coins</t>
+  </si>
+  <si>
+    <t>Pure Water Drop</t>
+  </si>
+  <si>
+    <t>Model Cost</t>
+  </si>
+  <si>
+    <t>Exploration</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +385,4253 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K102"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="12.21875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>250</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>INT(B$2 + ($A3 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>500</v>
+      </c>
+      <c r="C3">
+        <f>INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
+        <v>505</v>
+      </c>
+      <c r="D3">
+        <f>INT(D$2 + ($A3 - 1) * ((D$101 - D$2) / 99))</f>
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:H18" si="0">INT(E$2 + ($A3 - 1) * ((E$101 - E$2) / 99))</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" ref="A4:A67" si="1">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:G67" si="2">INT(B$2 + ($A4 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>750</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="2"/>
+        <v>1010</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <f>INT(I$3*(I$101/I$3)^(($A4-2)/98))</f>
+        <v>108</v>
+      </c>
+      <c r="J4">
+        <f>INT(J$3*(J$101/J$3)^(($A4-2)/98))</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="2"/>
+        <v>1515</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:J36" si="3">INT(I$3*(I$101/I$3)^(($A5-2)/98))</f>
+        <v>117</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="2"/>
+        <v>1250</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="2"/>
+        <v>2020</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="3"/>
+        <v>127</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="2"/>
+        <v>1500</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="2"/>
+        <v>2525</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>137</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="2"/>
+        <v>1750</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="2"/>
+        <v>3030</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>149</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="2"/>
+        <v>2000</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="2"/>
+        <v>3535</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>161</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="2"/>
+        <v>2250</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="2"/>
+        <v>4040</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>174</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="2"/>
+        <v>2500</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="2"/>
+        <v>4545</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="3"/>
+        <v>189</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="2"/>
+        <v>2750</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="2"/>
+        <v>5050</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="2"/>
+        <v>5555</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>222</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="2"/>
+        <v>3250</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="2"/>
+        <v>6060</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="2"/>
+        <v>6565</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="3"/>
+        <v>260</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="2"/>
+        <v>3750</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="2"/>
+        <v>7070</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="3"/>
+        <v>282</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="2"/>
+        <v>4000</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="2"/>
+        <v>7575</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="3"/>
+        <v>305</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="2"/>
+        <v>4250</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="2"/>
+        <v>8080</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="3"/>
+        <v>331</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="2"/>
+        <v>4500</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="2"/>
+        <v>8585</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <f t="shared" ref="G19:H82" si="4">INT(G$2 + ($A19 - 1) * ((G$101 - G$2) / 99))</f>
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="3"/>
+        <v>358</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="2"/>
+        <v>4750</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="2"/>
+        <v>9090</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="3"/>
+        <v>388</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="2"/>
+        <v>9595</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="3"/>
+        <v>420</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="2"/>
+        <v>5250</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="2"/>
+        <v>10101</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="3"/>
+        <v>455</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="2"/>
+        <v>5500</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="2"/>
+        <v>10606</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="3"/>
+        <v>493</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="2"/>
+        <v>5750</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="2"/>
+        <v>11111</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="2"/>
+        <v>115</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="3"/>
+        <v>534</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="2"/>
+        <v>11616</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="3"/>
+        <v>579</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="2"/>
+        <v>6250</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="2"/>
+        <v>12121</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="3"/>
+        <v>627</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="2"/>
+        <v>6500</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="2"/>
+        <v>12626</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="2"/>
+        <v>130</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="3"/>
+        <v>679</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+      <c r="K27">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="2"/>
+        <v>6750</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="2"/>
+        <v>13131</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="3"/>
+        <v>735</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="3"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="2"/>
+        <v>7000</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="2"/>
+        <v>13636</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="4"/>
+        <v>28</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="3"/>
+        <v>797</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="3"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="2"/>
+        <v>7250</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="2"/>
+        <v>14141</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="3"/>
+        <v>863</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="3"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="2"/>
+        <v>7500</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="2"/>
+        <v>14646</v>
+      </c>
+      <c r="D31">
+        <f t="shared" ref="D31:G62" si="5">INT(D$2 + ($A31 - 1) * ((D$101 - D$2) / 99))</f>
+        <v>150</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="3"/>
+        <v>935</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="3"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="2"/>
+        <v>7750</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="2"/>
+        <v>15151</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="5"/>
+        <v>155</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="3"/>
+        <v>1012</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="3"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="2"/>
+        <v>8000</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="2"/>
+        <v>15656</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="5"/>
+        <v>160</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="3"/>
+        <v>1096</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="3"/>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="2"/>
+        <v>8250</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="2"/>
+        <v>16161</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="5"/>
+        <v>165</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="3"/>
+        <v>1188</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="3"/>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="2"/>
+        <v>8500</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="2"/>
+        <v>16666</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="5"/>
+        <v>170</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="3"/>
+        <v>1286</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="3"/>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="2"/>
+        <v>8750</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="2"/>
+        <v>17171</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="5"/>
+        <v>175</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="3"/>
+        <v>1393</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="3"/>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="2"/>
+        <v>9000</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="2"/>
+        <v>17676</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="I37">
+        <f t="shared" ref="I37:J68" si="6">INT(I$3*(I$101/I$3)^(($A37-2)/98))</f>
+        <v>1509</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="6"/>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="2"/>
+        <v>9250</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="2"/>
+        <v>18181</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="5"/>
+        <v>185</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="6"/>
+        <v>1635</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="6"/>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="2"/>
+        <v>9500</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="2"/>
+        <v>18686</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="6"/>
+        <v>1771</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="6"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="2"/>
+        <v>9750</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="2"/>
+        <v>19191</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="5"/>
+        <v>195</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="6"/>
+        <v>1918</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="6"/>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="2"/>
+        <v>19696</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="6"/>
+        <v>2077</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="6"/>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="2"/>
+        <v>10250</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="2"/>
+        <v>20202</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="5"/>
+        <v>205</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="4"/>
+        <v>41</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="6"/>
+        <v>2250</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="6"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="2"/>
+        <v>10500</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="2"/>
+        <v>20707</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="4"/>
+        <v>42</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="6"/>
+        <v>2437</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="6"/>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="2"/>
+        <v>10750</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="2"/>
+        <v>21212</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="5"/>
+        <v>215</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="4"/>
+        <v>43</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="6"/>
+        <v>2639</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="6"/>
+        <v>527</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="2"/>
+        <v>11000</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="2"/>
+        <v>21717</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="6"/>
+        <v>2859</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="6"/>
+        <v>571</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="2"/>
+        <v>11250</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="2"/>
+        <v>22222</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="5"/>
+        <v>225</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="6"/>
+        <v>3096</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="6"/>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="2"/>
+        <v>11500</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="2"/>
+        <v>22727</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="6"/>
+        <v>3354</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="6"/>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="2"/>
+        <v>11750</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="2"/>
+        <v>23232</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="5"/>
+        <v>235</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="4"/>
+        <v>47</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="6"/>
+        <v>3633</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="6"/>
+        <v>726</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="2"/>
+        <v>12000</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="2"/>
+        <v>23737</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="5"/>
+        <v>240</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="6"/>
+        <v>3935</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="6"/>
+        <v>787</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="2"/>
+        <v>12250</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="2"/>
+        <v>24242</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="5"/>
+        <v>245</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="4"/>
+        <v>49</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="6"/>
+        <v>4262</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="6"/>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="2"/>
+        <v>12500</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="2"/>
+        <v>24747</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="5"/>
+        <v>250</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="6"/>
+        <v>4616</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="6"/>
+        <v>923</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="2"/>
+        <v>12750</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="2"/>
+        <v>25252</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="5"/>
+        <v>255</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="4"/>
+        <v>51</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="6"/>
+        <v>1000</v>
+      </c>
+      <c r="K52">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="2"/>
+        <v>13000</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="2"/>
+        <v>25757</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="5"/>
+        <v>260</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="4"/>
+        <v>52</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="6"/>
+        <v>5415</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="6"/>
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="2"/>
+        <v>13250</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="2"/>
+        <v>26262</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="5"/>
+        <v>265</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="4"/>
+        <v>53</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="6"/>
+        <v>5865</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="6"/>
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="2"/>
+        <v>13500</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="2"/>
+        <v>26767</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="5"/>
+        <v>270</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="4"/>
+        <v>54</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="6"/>
+        <v>6353</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="6"/>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="2"/>
+        <v>13750</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="2"/>
+        <v>27272</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="5"/>
+        <v>275</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="4"/>
+        <v>55</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="6"/>
+        <v>6881</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="6"/>
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="2"/>
+        <v>14000</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="2"/>
+        <v>27777</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="5"/>
+        <v>280</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="6"/>
+        <v>7453</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="6"/>
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="2"/>
+        <v>14250</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="2"/>
+        <v>28282</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="5"/>
+        <v>285</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="4"/>
+        <v>57</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="6"/>
+        <v>8072</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="6"/>
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="2"/>
+        <v>14500</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="2"/>
+        <v>28787</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="5"/>
+        <v>290</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="4"/>
+        <v>58</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="6"/>
+        <v>8743</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="6"/>
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="2"/>
+        <v>14750</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="2"/>
+        <v>29292</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="5"/>
+        <v>295</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="4"/>
+        <v>59</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="6"/>
+        <v>9470</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="6"/>
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="2"/>
+        <v>15000</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="2"/>
+        <v>29797</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="6"/>
+        <v>10257</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="6"/>
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="2"/>
+        <v>15250</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="2"/>
+        <v>30303</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="5"/>
+        <v>305</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="4"/>
+        <v>61</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="6"/>
+        <v>11109</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="6"/>
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="2"/>
+        <v>15500</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="2"/>
+        <v>30808</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ref="D63:H100" si="7">INT(D$2 + ($A63 - 1) * ((D$101 - D$2) / 99))</f>
+        <v>310</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="4"/>
+        <v>62</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="6"/>
+        <v>12032</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="6"/>
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="2"/>
+        <v>15750</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="2"/>
+        <v>31313</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="7"/>
+        <v>315</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="4"/>
+        <v>63</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="6"/>
+        <v>13032</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="6"/>
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="2"/>
+        <v>16000</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="2"/>
+        <v>31818</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="7"/>
+        <v>320</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="6"/>
+        <v>14116</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="6"/>
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="2"/>
+        <v>16250</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="2"/>
+        <v>32323</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="7"/>
+        <v>325</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="4"/>
+        <v>65</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="6"/>
+        <v>15289</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="6"/>
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <f t="shared" si="2"/>
+        <v>16500</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="2"/>
+        <v>32828</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="7"/>
+        <v>330</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="4"/>
+        <v>66</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="6"/>
+        <v>16560</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="6"/>
+        <v>3312</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <f t="shared" ref="A68:A101" si="8">A67+1</f>
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <f t="shared" ref="B68:D100" si="9">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
+        <v>16750</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="9"/>
+        <v>33333</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="7"/>
+        <v>335</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="4"/>
+        <v>67</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="6"/>
+        <v>17936</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="6"/>
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <f t="shared" si="8"/>
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="9"/>
+        <v>17000</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="9"/>
+        <v>33838</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="7"/>
+        <v>340</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ref="I69:J100" si="10">INT(I$3*(I$101/I$3)^(($A69-2)/98))</f>
+        <v>19427</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="10"/>
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <f t="shared" si="8"/>
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="9"/>
+        <v>17250</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="9"/>
+        <v>34343</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="7"/>
+        <v>345</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="4"/>
+        <v>69</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="10"/>
+        <v>21041</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="10"/>
+        <v>4208</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <f t="shared" si="8"/>
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="9"/>
+        <v>17500</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="9"/>
+        <v>34848</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="7"/>
+        <v>350</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="G71">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="10"/>
+        <v>22790</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="10"/>
+        <v>4558</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <f t="shared" si="8"/>
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="9"/>
+        <v>17750</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="9"/>
+        <v>35353</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="4"/>
+        <v>71</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="10"/>
+        <v>24684</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="10"/>
+        <v>4936</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="9"/>
+        <v>18000</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="9"/>
+        <v>35858</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="7"/>
+        <v>360</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="10"/>
+        <v>26736</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="10"/>
+        <v>5347</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <f t="shared" si="8"/>
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="9"/>
+        <v>18250</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="9"/>
+        <v>36363</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="7"/>
+        <v>365</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="4"/>
+        <v>73</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="10"/>
+        <v>28958</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="10"/>
+        <v>5791</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <f t="shared" si="8"/>
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="9"/>
+        <v>18500</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="9"/>
+        <v>36868</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="7"/>
+        <v>370</v>
+      </c>
+      <c r="E75">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="4"/>
+        <v>74</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="10"/>
+        <v>31365</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="10"/>
+        <v>6273</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="9"/>
+        <v>18750</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="9"/>
+        <v>37373</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="7"/>
+        <v>375</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="4"/>
+        <v>75</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="10"/>
+        <v>33971</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="10"/>
+        <v>6794</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <f t="shared" si="8"/>
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <f t="shared" si="9"/>
+        <v>19000</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="9"/>
+        <v>37878</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="7"/>
+        <v>380</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="4"/>
+        <v>76</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="10"/>
+        <v>36795</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="10"/>
+        <v>7359</v>
+      </c>
+      <c r="K77">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <f t="shared" si="8"/>
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="9"/>
+        <v>19250</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="9"/>
+        <v>38383</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="7"/>
+        <v>385</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="4"/>
+        <v>77</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="10"/>
+        <v>39853</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="10"/>
+        <v>7970</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <f t="shared" si="8"/>
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="9"/>
+        <v>19500</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="9"/>
+        <v>38888</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="7"/>
+        <v>390</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="4"/>
+        <v>78</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="10"/>
+        <v>43165</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="10"/>
+        <v>8633</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <f t="shared" si="8"/>
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="9"/>
+        <v>19750</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="9"/>
+        <v>39393</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="7"/>
+        <v>395</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="4"/>
+        <v>79</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="10"/>
+        <v>46753</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="10"/>
+        <v>9350</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="9"/>
+        <v>20000</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="9"/>
+        <v>39898</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="7"/>
+        <v>400</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="4"/>
+        <v>80</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="10"/>
+        <v>50638</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="10"/>
+        <v>10127</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <f t="shared" si="8"/>
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="9"/>
+        <v>20250</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="9"/>
+        <v>40404</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="7"/>
+        <v>405</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="4"/>
+        <v>81</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="10"/>
+        <v>54847</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="10"/>
+        <v>10969</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <f t="shared" si="8"/>
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <f t="shared" si="9"/>
+        <v>20500</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="9"/>
+        <v>40909</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="7"/>
+        <v>410</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="7"/>
+        <v>82</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="10"/>
+        <v>59405</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="10"/>
+        <v>11881</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <f t="shared" si="8"/>
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="9"/>
+        <v>20750</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="9"/>
+        <v>41414</v>
+      </c>
+      <c r="D84">
+        <f t="shared" si="7"/>
+        <v>415</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="7"/>
+        <v>83</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="10"/>
+        <v>64343</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="10"/>
+        <v>12868</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <f t="shared" si="8"/>
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <f t="shared" si="9"/>
+        <v>21000</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="9"/>
+        <v>41919</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="7"/>
+        <v>420</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="7"/>
+        <v>84</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="10"/>
+        <v>69690</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="10"/>
+        <v>13938</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <f t="shared" si="8"/>
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <f t="shared" si="9"/>
+        <v>21250</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="9"/>
+        <v>42424</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="7"/>
+        <v>425</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="G86">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="7"/>
+        <v>85</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="10"/>
+        <v>75482</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="10"/>
+        <v>15096</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <f t="shared" si="8"/>
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <f t="shared" si="9"/>
+        <v>21500</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="9"/>
+        <v>42929</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="7"/>
+        <v>430</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="7"/>
+        <v>86</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="10"/>
+        <v>81756</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="10"/>
+        <v>16351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <f t="shared" si="8"/>
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <f t="shared" si="9"/>
+        <v>21750</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="9"/>
+        <v>43434</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="7"/>
+        <v>435</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="G88">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="7"/>
+        <v>87</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="10"/>
+        <v>88550</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="10"/>
+        <v>17710</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <f t="shared" si="8"/>
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <f t="shared" si="9"/>
+        <v>22000</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="9"/>
+        <v>43939</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="7"/>
+        <v>440</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="G89">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="7"/>
+        <v>88</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="10"/>
+        <v>95910</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="10"/>
+        <v>19182</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <f t="shared" si="8"/>
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <f t="shared" si="9"/>
+        <v>22250</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="9"/>
+        <v>44444</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="7"/>
+        <v>445</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="7"/>
+        <v>89</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="10"/>
+        <v>103881</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="10"/>
+        <v>20776</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <f t="shared" si="8"/>
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <f t="shared" si="9"/>
+        <v>22500</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="9"/>
+        <v>44949</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="7"/>
+        <v>450</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="G91">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="7"/>
+        <v>90</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="10"/>
+        <v>112515</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="10"/>
+        <v>22503</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <f t="shared" si="8"/>
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <f t="shared" si="9"/>
+        <v>22750</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="9"/>
+        <v>45454</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="7"/>
+        <v>455</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="7"/>
+        <v>27</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="7"/>
+        <v>91</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="10"/>
+        <v>121866</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="10"/>
+        <v>24373</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <f t="shared" si="9"/>
+        <v>23000</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="9"/>
+        <v>45959</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="7"/>
+        <v>460</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="7"/>
+        <v>27</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="7"/>
+        <v>92</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="10"/>
+        <v>131994</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="10"/>
+        <v>26398</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <f t="shared" si="8"/>
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <f t="shared" si="9"/>
+        <v>23250</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="9"/>
+        <v>46464</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="7"/>
+        <v>465</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="7"/>
+        <v>27</v>
+      </c>
+      <c r="G94">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="7"/>
+        <v>93</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="10"/>
+        <v>142965</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="10"/>
+        <v>28593</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <f t="shared" si="8"/>
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <f t="shared" si="9"/>
+        <v>23500</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="9"/>
+        <v>46969</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="7"/>
+        <v>470</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="7"/>
+        <v>94</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="10"/>
+        <v>154847</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="10"/>
+        <v>30969</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <f t="shared" si="8"/>
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <f t="shared" si="9"/>
+        <v>23750</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="9"/>
+        <v>47474</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="7"/>
+        <v>475</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="G96">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="7"/>
+        <v>95</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="10"/>
+        <v>167716</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="10"/>
+        <v>33543</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <f t="shared" si="9"/>
+        <v>24000</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="9"/>
+        <v>47979</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="7"/>
+        <v>480</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="G97">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="7"/>
+        <v>96</v>
+      </c>
+      <c r="I97">
+        <f t="shared" si="10"/>
+        <v>181655</v>
+      </c>
+      <c r="J97">
+        <f t="shared" si="10"/>
+        <v>36331</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <f t="shared" si="8"/>
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <f t="shared" si="9"/>
+        <v>24250</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="9"/>
+        <v>48484</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="7"/>
+        <v>485</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="G98">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="7"/>
+        <v>97</v>
+      </c>
+      <c r="I98">
+        <f t="shared" si="10"/>
+        <v>196753</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="10"/>
+        <v>39350</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <f t="shared" si="8"/>
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <f t="shared" si="9"/>
+        <v>24500</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="9"/>
+        <v>48989</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="7"/>
+        <v>490</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="G99">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="7"/>
+        <v>98</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="10"/>
+        <v>213105</v>
+      </c>
+      <c r="J99">
+        <f t="shared" si="10"/>
+        <v>42621</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <f t="shared" si="8"/>
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <f t="shared" si="9"/>
+        <v>24750</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="9"/>
+        <v>49494</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="7"/>
+        <v>495</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="G100">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="7"/>
+        <v>99</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="10"/>
+        <v>230816</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="10"/>
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>25000</v>
+      </c>
+      <c r="C101">
+        <v>50000</v>
+      </c>
+      <c r="D101">
+        <v>500</v>
+      </c>
+      <c r="E101">
+        <v>10</v>
+      </c>
+      <c r="F101">
+        <v>30</v>
+      </c>
+      <c r="G101">
+        <v>10</v>
+      </c>
+      <c r="H101">
+        <v>100</v>
+      </c>
+      <c r="I101">
+        <v>250000</v>
+      </c>
+      <c r="J101">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I102">
+        <f>SUM(I2:I101)</f>
+        <v>3256791</v>
+      </c>
+      <c r="J102">
+        <f>SUM(J2:J101)</f>
+        <v>651325</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/Ressources/Stats/Crew_stats.xlsx
+++ b/Assets/Ressources/Stats/Crew_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10609BD0-D3E6-4898-94A8-A1CB9524523A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEB0242-5CBA-49FE-AA3B-8000AFE3988A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,12 +84,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -104,8 +128,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,25 +427,25 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I1" t="s">
@@ -462,7 +490,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -511,7 +539,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:G67" si="2">INT(B$2 + ($A4 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B4:F67" si="2">INT(B$2 + ($A4 - 1) * ((B$101 - B$2) / 99))</f>
         <v>750</v>
       </c>
       <c r="C4">
@@ -1513,7 +1541,7 @@
         <v>135</v>
       </c>
       <c r="K27">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -1656,7 +1684,7 @@
         <v>14646</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31:G62" si="5">INT(D$2 + ($A31 - 1) * ((D$101 - D$2) / 99))</f>
+        <f t="shared" ref="D31:F62" si="5">INT(D$2 + ($A31 - 1) * ((D$101 - D$2) / 99))</f>
         <v>150</v>
       </c>
       <c r="E31">
@@ -2566,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="K52">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
@@ -3205,7 +3233,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <f t="shared" ref="B68:D100" si="9">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
+        <f t="shared" ref="B68:C100" si="9">INT(B$2 + ($A68 - 1) * ((B$101 - B$2) / 99))</f>
         <v>16750</v>
       </c>
       <c r="C68">
@@ -3619,7 +3647,7 @@
         <v>7359</v>
       </c>
       <c r="K77">
-        <v>10000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">

--- a/Assets/Ressources/Stats/Crew_stats.xlsx
+++ b/Assets/Ressources/Stats/Crew_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEB0242-5CBA-49FE-AA3B-8000AFE3988A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A4F37F-CAD9-41B2-AED1-8C9110E73135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -414,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="12.21875" customWidth="1"/>
@@ -4649,16 +4649,6 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="I102">
-        <f>SUM(I2:I101)</f>
-        <v>3256791</v>
-      </c>
-      <c r="J102">
-        <f>SUM(J2:J101)</f>
-        <v>651325</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
